--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>136079033</v>
       </c>
       <c r="B37" t="n">
-        <v>92769</v>
+        <v>92772</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>136079022</v>
       </c>
       <c r="B43" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>136079035</v>
       </c>
       <c r="B44" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>136079136</v>
       </c>
       <c r="B45" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>136400079</v>
       </c>
       <c r="B46" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>136011248</v>
       </c>
       <c r="B72" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>136011257</v>
       </c>
       <c r="B73" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>136079009</v>
       </c>
       <c r="B74" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>136079025</v>
       </c>
       <c r="B75" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>136079032</v>
       </c>
       <c r="B76" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>136079036</v>
       </c>
       <c r="B77" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97670</v>
+        <v>97673</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>136011253</v>
       </c>
       <c r="B127" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>136079018</v>
       </c>
       <c r="B128" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>136079024</v>
       </c>
       <c r="B129" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>136079026</v>
       </c>
       <c r="B130" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>136079028</v>
       </c>
       <c r="B131" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>136079039</v>
       </c>
       <c r="B132" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>136079040</v>
       </c>
       <c r="B133" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>136079015</v>
       </c>
       <c r="B137" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>136079014</v>
       </c>
       <c r="B389" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>136079384</v>
       </c>
       <c r="B391" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>136079385</v>
       </c>
       <c r="B392" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>136079389</v>
       </c>
       <c r="B393" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>136079390</v>
       </c>
       <c r="B394" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>136400085</v>
       </c>
       <c r="B396" t="n">
-        <v>98393</v>
+        <v>98396</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>136011269</v>
       </c>
       <c r="B404" t="n">
-        <v>92448</v>
+        <v>92451</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>136079033</v>
       </c>
       <c r="B37" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>136079009</v>
       </c>
       <c r="B74" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>136079025</v>
       </c>
       <c r="B75" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>136079032</v>
       </c>
       <c r="B76" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>136079036</v>
       </c>
       <c r="B77" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97673</v>
+        <v>97674</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>136079018</v>
       </c>
       <c r="B128" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>136079024</v>
       </c>
       <c r="B129" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>136079026</v>
       </c>
       <c r="B130" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>136079028</v>
       </c>
       <c r="B131" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>136079039</v>
       </c>
       <c r="B132" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>136079040</v>
       </c>
       <c r="B133" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>136079015</v>
       </c>
       <c r="B137" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>136079014</v>
       </c>
       <c r="B389" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>136079384</v>
       </c>
       <c r="B391" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>136079385</v>
       </c>
       <c r="B392" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>136079389</v>
       </c>
       <c r="B393" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>136079390</v>
       </c>
       <c r="B394" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>136400085</v>
       </c>
       <c r="B396" t="n">
-        <v>98396</v>
+        <v>98397</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>136400083</v>
       </c>
       <c r="B14" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>136400087</v>
       </c>
       <c r="B15" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>136671317</v>
       </c>
       <c r="B16" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136400086</v>
       </c>
       <c r="B18" t="n">
-        <v>83446</v>
+        <v>83448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>136671316</v>
       </c>
       <c r="B36" t="n">
-        <v>83453</v>
+        <v>83455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>136400079</v>
       </c>
       <c r="B46" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97674</v>
+        <v>97679</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>136400076</v>
       </c>
       <c r="B178" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>136400077</v>
       </c>
       <c r="B179" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>136400078</v>
       </c>
       <c r="B180" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>136400080</v>
       </c>
       <c r="B181" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>136400084</v>
       </c>
       <c r="B182" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>136400081</v>
       </c>
       <c r="B234" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>136400075</v>
       </c>
       <c r="B265" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>136400082</v>
       </c>
       <c r="B266" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>136671315</v>
       </c>
       <c r="B382" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>136400085</v>
       </c>
       <c r="B396" t="n">
-        <v>98397</v>
+        <v>98402</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>136400079</v>
       </c>
       <c r="B46" t="n">
-        <v>89472</v>
+        <v>89474</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89472</v>
+        <v>89474</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97679</v>
+        <v>97681</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>136400085</v>
       </c>
       <c r="B396" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>136400083</v>
       </c>
       <c r="B14" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>136400087</v>
       </c>
       <c r="B15" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>136671317</v>
       </c>
       <c r="B16" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136400086</v>
       </c>
       <c r="B18" t="n">
-        <v>83448</v>
+        <v>83452</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>136671316</v>
       </c>
       <c r="B36" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>136400079</v>
       </c>
       <c r="B46" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97681</v>
+        <v>97687</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>136400076</v>
       </c>
       <c r="B178" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>136400077</v>
       </c>
       <c r="B179" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>136400078</v>
       </c>
       <c r="B180" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>136400080</v>
       </c>
       <c r="B181" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>136400084</v>
       </c>
       <c r="B182" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>136400081</v>
       </c>
       <c r="B234" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>136400075</v>
       </c>
       <c r="B265" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>136400082</v>
       </c>
       <c r="B266" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>136400085</v>
       </c>
       <c r="B396" t="n">
-        <v>98404</v>
+        <v>98410</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>136400083</v>
       </c>
       <c r="B14" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>136400087</v>
       </c>
       <c r="B15" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>136671317</v>
       </c>
       <c r="B16" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136400086</v>
       </c>
       <c r="B18" t="n">
-        <v>83452</v>
+        <v>83454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>136671316</v>
       </c>
       <c r="B36" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>136400079</v>
       </c>
       <c r="B46" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97687</v>
+        <v>97689</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>136400076</v>
       </c>
       <c r="B178" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>136400077</v>
       </c>
       <c r="B179" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>136400078</v>
       </c>
       <c r="B180" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>136400080</v>
       </c>
       <c r="B181" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>136400084</v>
       </c>
       <c r="B182" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>136400081</v>
       </c>
       <c r="B234" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>136400075</v>
       </c>
       <c r="B265" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>136400082</v>
       </c>
       <c r="B266" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>136400085</v>
       </c>
       <c r="B396" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>136400083</v>
       </c>
       <c r="B14" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>136400087</v>
       </c>
       <c r="B15" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>136671317</v>
       </c>
       <c r="B16" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136400086</v>
       </c>
       <c r="B18" t="n">
-        <v>83454</v>
+        <v>83455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>136671316</v>
       </c>
       <c r="B36" t="n">
-        <v>83461</v>
+        <v>83462</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>136400079</v>
       </c>
       <c r="B46" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97689</v>
+        <v>97690</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>136400076</v>
       </c>
       <c r="B178" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>136400077</v>
       </c>
       <c r="B179" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>136400078</v>
       </c>
       <c r="B180" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>136400080</v>
       </c>
       <c r="B181" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>136400084</v>
       </c>
       <c r="B182" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>136400081</v>
       </c>
       <c r="B234" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>136400075</v>
       </c>
       <c r="B265" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>136400082</v>
       </c>
       <c r="B266" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>136400085</v>
       </c>
       <c r="B396" t="n">
-        <v>98412</v>
+        <v>98413</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97690</v>
+        <v>97696</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>136671317</v>
       </c>
       <c r="B16" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>136671316</v>
       </c>
       <c r="B36" t="n">
-        <v>83462</v>
+        <v>83466</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97696</v>
+        <v>97700</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97700</v>
+        <v>97702</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>136671317</v>
       </c>
       <c r="B16" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>136671316</v>
       </c>
       <c r="B36" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>136671317</v>
       </c>
       <c r="B16" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>136671316</v>
       </c>
       <c r="B36" t="n">
-        <v>83468</v>
+        <v>83481</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97704</v>
+        <v>97717</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>136671315</v>
       </c>
       <c r="B382" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>136671317</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>136671316</v>
       </c>
       <c r="B36" t="n">
-        <v>83481</v>
+        <v>83483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97717</v>
+        <v>97719</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>136671315</v>
       </c>
       <c r="B382" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -43099,11 +43099,7 @@
       </c>
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr"/>
-      <c r="M382" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M382" t="inlineStr"/>
       <c r="N382" t="inlineStr"/>
       <c r="P382" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>136671320</v>
       </c>
       <c r="B5" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>136671316</v>
       </c>
       <c r="B36" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136671318</v>
       </c>
       <c r="B47" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>136400058</v>
       </c>
       <c r="B81" t="n">
-        <v>97719</v>
+        <v>97722</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
